--- a/public/templates/drivebonus_template.xlsx
+++ b/public/templates/drivebonus_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\wordtoexcel\staff_manager\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BCF40F-C7CB-49DD-9A4E-E9774BE0742C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{121A8E1C-6EC0-466B-81B6-BA4564DEB0D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{FE9DB102-5480-4C6F-9AE4-967FBD7E5687}"/>
+    <workbookView xWindow="1245" yWindow="750" windowWidth="27150" windowHeight="18705" activeTab="1" xr2:uid="{FE9DB102-5480-4C6F-9AE4-967FBD7E5687}"/>
   </bookViews>
   <sheets>
     <sheet name="正駕" sheetId="1" r:id="rId1"/>
@@ -282,9 +282,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>承辦人</t>
-  </si>
-  <si>
     <t>區隊長</t>
   </si>
   <si>
@@ -322,6 +319,10 @@
   </si>
   <si>
     <t>____{{year}}____年_{{month}}_月份</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>領班長</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -851,6 +852,33 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -911,40 +939,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1274,153 +1275,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="27" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
-      <c r="AL1" s="29"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="38"/>
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="32"/>
+      <c r="A2" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="41"/>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="40"/>
-      <c r="AB3" s="40"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="40"/>
-      <c r="AE3" s="40"/>
-      <c r="AF3" s="40"/>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="42" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="50"/>
+      <c r="AI3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="AJ3" s="42" t="s">
+      <c r="AJ3" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="42" t="s">
+      <c r="AK3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="44" t="s">
+      <c r="AL3" s="53" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="34"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="38"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="47"/>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -1452,20 +1453,20 @@
       <c r="AF4" s="2"/>
       <c r="AG4" s="2"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="43"/>
-      <c r="AJ4" s="43"/>
-      <c r="AK4" s="43"/>
-      <c r="AL4" s="45"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="52"/>
+      <c r="AK4" s="52"/>
+      <c r="AL4" s="54"/>
     </row>
     <row r="5" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="57" t="s">
-        <v>24</v>
+      <c r="A5" s="26" t="s">
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -1508,7 +1509,7 @@
       <c r="AL5" s="7"/>
     </row>
     <row r="6" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="57"/>
+      <c r="A6" s="26"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="6"/>
@@ -1552,7 +1553,7 @@
       <c r="AL6" s="7"/>
     </row>
     <row r="7" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="57"/>
+      <c r="A7" s="26"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="6"/>
@@ -1596,7 +1597,7 @@
       <c r="AL7" s="7"/>
     </row>
     <row r="8" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="57"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="6"/>
@@ -1640,7 +1641,7 @@
       <c r="AL8" s="7"/>
     </row>
     <row r="9" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="57"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="6"/>
@@ -1684,7 +1685,7 @@
       <c r="AL9" s="7"/>
     </row>
     <row r="10" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="57"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="6"/>
@@ -1728,7 +1729,7 @@
       <c r="AL10" s="7"/>
     </row>
     <row r="11" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="57"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="6"/>
@@ -1772,7 +1773,7 @@
       <c r="AL11" s="7"/>
     </row>
     <row r="12" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="57"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="6"/>
@@ -1816,7 +1817,7 @@
       <c r="AL12" s="7"/>
     </row>
     <row r="13" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="57"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="6"/>
@@ -1860,7 +1861,7 @@
       <c r="AL13" s="7"/>
     </row>
     <row r="14" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="57"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="6"/>
@@ -1904,86 +1905,86 @@
       <c r="AL14" s="7"/>
     </row>
     <row r="15" spans="1:38" s="8" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="46" t="s">
+      <c r="A15" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="47"/>
-      <c r="Q15" s="47"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="47"/>
-      <c r="T15" s="47"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="47"/>
-      <c r="W15" s="47"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="47"/>
-      <c r="Z15" s="47"/>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="47"/>
-      <c r="AC15" s="47"/>
-      <c r="AD15" s="47"/>
-      <c r="AE15" s="47"/>
-      <c r="AF15" s="47"/>
-      <c r="AG15" s="47"/>
-      <c r="AH15" s="47"/>
-      <c r="AI15" s="47"/>
-      <c r="AJ15" s="47"/>
-      <c r="AK15" s="47"/>
-      <c r="AL15" s="48"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="28"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="28"/>
+      <c r="AJ15" s="28"/>
+      <c r="AK15" s="28"/>
+      <c r="AL15" s="29"/>
     </row>
     <row r="16" spans="1:38" s="8" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="49"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50"/>
-      <c r="S16" s="50"/>
-      <c r="T16" s="50"/>
-      <c r="U16" s="50"/>
-      <c r="V16" s="50"/>
-      <c r="W16" s="50"/>
-      <c r="X16" s="50"/>
-      <c r="Y16" s="50"/>
-      <c r="Z16" s="50"/>
-      <c r="AA16" s="50"/>
-      <c r="AB16" s="50"/>
-      <c r="AC16" s="50"/>
-      <c r="AD16" s="50"/>
-      <c r="AE16" s="50"/>
-      <c r="AF16" s="50"/>
-      <c r="AG16" s="50"/>
-      <c r="AH16" s="50"/>
-      <c r="AI16" s="50"/>
-      <c r="AJ16" s="50"/>
-      <c r="AK16" s="50"/>
-      <c r="AL16" s="51"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="31"/>
+      <c r="AE16" s="31"/>
+      <c r="AF16" s="31"/>
+      <c r="AG16" s="31"/>
+      <c r="AH16" s="31"/>
+      <c r="AI16" s="31"/>
+      <c r="AJ16" s="31"/>
+      <c r="AK16" s="31"/>
+      <c r="AL16" s="32"/>
     </row>
     <row r="17" spans="1:38" s="12" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="9" t="s">
@@ -1991,62 +1992,56 @@
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="10" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="I17" s="52"/>
-      <c r="J17" s="52"/>
+      <c r="H17" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q17" s="52"/>
-      <c r="R17" s="52"/>
+      <c r="P17" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
-      <c r="V17" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="W17" s="52"/>
-      <c r="X17" s="52"/>
+      <c r="V17" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
       <c r="Y17" s="11"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
-      <c r="AB17" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC17" s="52"/>
-      <c r="AD17" s="52"/>
+      <c r="AB17" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC17" s="33"/>
+      <c r="AD17" s="33"/>
       <c r="AE17" s="11"/>
       <c r="AF17" s="11"/>
       <c r="AG17" s="11"/>
-      <c r="AH17" s="52" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI17" s="53"/>
+      <c r="AH17" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI17" s="34"/>
       <c r="AJ17" s="10"/>
       <c r="AK17" s="10"/>
       <c r="AL17" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A15:AL16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="AB17:AD17"/>
-    <mergeCell ref="AH17:AI17"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="X1:AL2"/>
     <mergeCell ref="A2:W2"/>
@@ -2058,6 +2053,12 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="A15:AL16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="AB17:AD17"/>
+    <mergeCell ref="AH17:AI17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2086,153 +2087,153 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
-      <c r="W1" s="26"/>
-      <c r="X1" s="27" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="28"/>
-      <c r="Z1" s="28"/>
-      <c r="AA1" s="28"/>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
-      <c r="AF1" s="28"/>
-      <c r="AG1" s="28"/>
-      <c r="AH1" s="28"/>
-      <c r="AI1" s="28"/>
-      <c r="AJ1" s="28"/>
-      <c r="AK1" s="28"/>
-      <c r="AL1" s="29"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="38"/>
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="26"/>
-      <c r="V2" s="26"/>
-      <c r="W2" s="26"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="31"/>
-      <c r="AA2" s="31"/>
-      <c r="AB2" s="31"/>
-      <c r="AC2" s="31"/>
-      <c r="AD2" s="31"/>
-      <c r="AE2" s="31"/>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="32"/>
+      <c r="A2" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="41"/>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="40"/>
-      <c r="W3" s="40"/>
-      <c r="X3" s="40"/>
-      <c r="Y3" s="40"/>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="40"/>
-      <c r="AB3" s="40"/>
-      <c r="AC3" s="40"/>
-      <c r="AD3" s="40"/>
-      <c r="AE3" s="40"/>
-      <c r="AF3" s="40"/>
-      <c r="AG3" s="40"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="43" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="49"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="50"/>
+      <c r="AI3" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="AJ3" s="54" t="s">
+      <c r="AJ3" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="42" t="s">
+      <c r="AK3" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="44" t="s">
+      <c r="AL3" s="53" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="34"/>
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -2264,20 +2265,20 @@
       <c r="AF4" s="2"/>
       <c r="AG4" s="25"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="43"/>
-      <c r="AJ4" s="55"/>
-      <c r="AK4" s="43"/>
-      <c r="AL4" s="45"/>
+      <c r="AI4" s="52"/>
+      <c r="AJ4" s="57"/>
+      <c r="AK4" s="52"/>
+      <c r="AL4" s="54"/>
     </row>
     <row r="5" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="24"/>
       <c r="E5" s="24"/>
@@ -3244,86 +3245,86 @@
       <c r="AL26" s="7"/>
     </row>
     <row r="27" spans="1:38" s="8" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="46" t="s">
+      <c r="A27" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="47"/>
-      <c r="T27" s="47"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="47"/>
-      <c r="W27" s="47"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="47"/>
-      <c r="Z27" s="47"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="47"/>
-      <c r="AC27" s="47"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="47"/>
-      <c r="AF27" s="47"/>
-      <c r="AG27" s="47"/>
-      <c r="AH27" s="47"/>
-      <c r="AI27" s="47"/>
-      <c r="AJ27" s="47"/>
-      <c r="AK27" s="47"/>
-      <c r="AL27" s="48"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+      <c r="AC27" s="28"/>
+      <c r="AD27" s="28"/>
+      <c r="AE27" s="28"/>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="28"/>
+      <c r="AH27" s="28"/>
+      <c r="AI27" s="28"/>
+      <c r="AJ27" s="28"/>
+      <c r="AK27" s="28"/>
+      <c r="AL27" s="29"/>
     </row>
     <row r="28" spans="1:38" s="8" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50"/>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="50"/>
-      <c r="AA28" s="50"/>
-      <c r="AB28" s="50"/>
-      <c r="AC28" s="50"/>
-      <c r="AD28" s="50"/>
-      <c r="AE28" s="50"/>
-      <c r="AF28" s="50"/>
-      <c r="AG28" s="50"/>
-      <c r="AH28" s="50"/>
-      <c r="AI28" s="50"/>
-      <c r="AJ28" s="50"/>
-      <c r="AK28" s="50"/>
-      <c r="AL28" s="51"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="32"/>
     </row>
     <row r="29" spans="1:38" s="12" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9" t="s">
@@ -3331,67 +3332,61 @@
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="10" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
+      <c r="H29" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
       <c r="O29" s="11"/>
-      <c r="P29" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="Q29" s="52"/>
-      <c r="R29" s="52"/>
+      <c r="P29" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
       <c r="S29" s="11"/>
       <c r="T29" s="11"/>
       <c r="U29" s="11"/>
-      <c r="V29" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="W29" s="52"/>
-      <c r="X29" s="52"/>
+      <c r="V29" s="33" t="s">
+        <v>16</v>
+      </c>
+      <c r="W29" s="33"/>
+      <c r="X29" s="33"/>
       <c r="Y29" s="11"/>
       <c r="Z29" s="11"/>
       <c r="AA29" s="11"/>
-      <c r="AB29" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="AC29" s="52"/>
-      <c r="AD29" s="52"/>
+      <c r="AB29" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC29" s="33"/>
+      <c r="AD29" s="33"/>
       <c r="AE29" s="11"/>
       <c r="AF29" s="11"/>
       <c r="AG29" s="11"/>
-      <c r="AH29" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="AI29" s="56"/>
+      <c r="AH29" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI29" s="55"/>
       <c r="AJ29" s="10"/>
       <c r="AK29" s="10"/>
       <c r="AL29" s="10"/>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A27:AL28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="AB29:AD29"/>
-    <mergeCell ref="AH29:AI29"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="X1:AL2"/>
     <mergeCell ref="A2:W2"/>
@@ -3403,6 +3398,12 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="A27:AL28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="AB29:AD29"/>
+    <mergeCell ref="AH29:AI29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/public/templates/drivebonus_template.xlsx
+++ b/public/templates/drivebonus_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\wordtoexcel\staff_manager\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFB8E65-E0F0-4822-A652-3F98131D81B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7288ACB7-B75E-418A-A5D0-43F534C06BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1" xr2:uid="{FE9DB102-5480-4C6F-9AE4-967FBD7E5687}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{FE9DB102-5480-4C6F-9AE4-967FBD7E5687}"/>
   </bookViews>
   <sheets>
     <sheet name="正駕" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="27">
   <si>
     <t>新北市政府環境保護局新店區清潔隊 隊員 駕駛安全獎金印領清冊</t>
   </si>
@@ -315,10 +315,6 @@
   </si>
   <si>
     <t>{{emp_id}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>____{{year}}____年_{{month}}_月份</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1324,7 +1320,7 @@
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -1996,7 +1992,7 @@
       </c>
       <c r="B17" s="9"/>
       <c r="C17" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
@@ -2136,7 +2132,7 @@
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -3336,7 +3332,7 @@
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" s="10"/>
       <c r="E29" s="10"/>

--- a/public/templates/drivebonus_template.xlsx
+++ b/public/templates/drivebonus_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\wordtoexcel\staff_manager\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7288ACB7-B75E-418A-A5D0-43F534C06BBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A8B72E-3DBC-47F9-B1F9-B7D9204950A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{FE9DB102-5480-4C6F-9AE4-967FBD7E5687}"/>
   </bookViews>
@@ -541,19 +541,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right/>
       <top style="medium">
         <color indexed="64"/>
@@ -783,6 +770,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -790,22 +790,22 @@
   <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -815,45 +815,69 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -879,20 +903,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="5"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="5"/>
@@ -900,52 +924,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="5"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="5"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1275,151 +1275,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="28" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="30"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="38"/>
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="33"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="41"/>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="43" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AJ3" s="43" t="s">
+      <c r="AJ3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="43" t="s">
+      <c r="AK3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="45" t="s">
+      <c r="AL3" s="52" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="35"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="39"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1453,10 +1453,10 @@
       <c r="AF4" s="2"/>
       <c r="AG4" s="2"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="44"/>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="46"/>
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="51"/>
+      <c r="AK4" s="51"/>
+      <c r="AL4" s="53"/>
     </row>
     <row r="5" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="26" t="s">
@@ -1905,86 +1905,86 @@
       <c r="AL14" s="7"/>
     </row>
     <row r="15" spans="1:38" s="8" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="48"/>
-      <c r="P15" s="48"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="48"/>
-      <c r="S15" s="48"/>
-      <c r="T15" s="48"/>
-      <c r="U15" s="48"/>
-      <c r="V15" s="48"/>
-      <c r="W15" s="48"/>
-      <c r="X15" s="48"/>
-      <c r="Y15" s="48"/>
-      <c r="Z15" s="48"/>
-      <c r="AA15" s="48"/>
-      <c r="AB15" s="48"/>
-      <c r="AC15" s="48"/>
-      <c r="AD15" s="48"/>
-      <c r="AE15" s="48"/>
-      <c r="AF15" s="48"/>
-      <c r="AG15" s="48"/>
-      <c r="AH15" s="48"/>
-      <c r="AI15" s="48"/>
-      <c r="AJ15" s="48"/>
-      <c r="AK15" s="48"/>
-      <c r="AL15" s="49"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="28"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="28"/>
+      <c r="J15" s="28"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="28"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="28"/>
+      <c r="AJ15" s="28"/>
+      <c r="AK15" s="28"/>
+      <c r="AL15" s="29"/>
     </row>
     <row r="16" spans="1:38" s="8" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="50"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="51"/>
-      <c r="L16" s="51"/>
-      <c r="M16" s="51"/>
-      <c r="N16" s="51"/>
-      <c r="O16" s="51"/>
-      <c r="P16" s="51"/>
-      <c r="Q16" s="51"/>
-      <c r="R16" s="51"/>
-      <c r="S16" s="51"/>
-      <c r="T16" s="51"/>
-      <c r="U16" s="51"/>
-      <c r="V16" s="51"/>
-      <c r="W16" s="51"/>
-      <c r="X16" s="51"/>
-      <c r="Y16" s="51"/>
-      <c r="Z16" s="51"/>
-      <c r="AA16" s="51"/>
-      <c r="AB16" s="51"/>
-      <c r="AC16" s="51"/>
-      <c r="AD16" s="51"/>
-      <c r="AE16" s="51"/>
-      <c r="AF16" s="51"/>
-      <c r="AG16" s="51"/>
-      <c r="AH16" s="51"/>
-      <c r="AI16" s="51"/>
-      <c r="AJ16" s="51"/>
-      <c r="AK16" s="51"/>
-      <c r="AL16" s="52"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="31"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="31"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="31"/>
+      <c r="AE16" s="31"/>
+      <c r="AF16" s="31"/>
+      <c r="AG16" s="31"/>
+      <c r="AH16" s="31"/>
+      <c r="AI16" s="31"/>
+      <c r="AJ16" s="31"/>
+      <c r="AK16" s="31"/>
+      <c r="AL16" s="32"/>
     </row>
     <row r="17" spans="1:38" s="12" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="9" t="s">
@@ -1998,56 +1998,50 @@
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="53" t="s">
+      <c r="H17" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="53"/>
-      <c r="J17" s="53"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="53" t="s">
+      <c r="P17" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="Q17" s="53"/>
-      <c r="R17" s="53"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
-      <c r="V17" s="53" t="s">
+      <c r="V17" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="W17" s="53"/>
-      <c r="X17" s="53"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
       <c r="Y17" s="11"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
-      <c r="AB17" s="53" t="s">
+      <c r="AB17" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="AC17" s="53"/>
-      <c r="AD17" s="53"/>
+      <c r="AC17" s="33"/>
+      <c r="AD17" s="33"/>
       <c r="AE17" s="11"/>
       <c r="AF17" s="11"/>
       <c r="AG17" s="11"/>
-      <c r="AH17" s="53" t="s">
+      <c r="AH17" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="AI17" s="54"/>
+      <c r="AI17" s="34"/>
       <c r="AJ17" s="10"/>
       <c r="AK17" s="10"/>
       <c r="AL17" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A15:AL16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="AB17:AD17"/>
-    <mergeCell ref="AH17:AI17"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="X1:AL2"/>
     <mergeCell ref="A2:W2"/>
@@ -2059,6 +2053,12 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="A15:AL16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="AB17:AD17"/>
+    <mergeCell ref="AH17:AI17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2087,151 +2087,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="28" t="s">
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="35"/>
+      <c r="X1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="30"/>
+      <c r="Y1" s="37"/>
+      <c r="Z1" s="37"/>
+      <c r="AA1" s="37"/>
+      <c r="AB1" s="37"/>
+      <c r="AC1" s="37"/>
+      <c r="AD1" s="37"/>
+      <c r="AE1" s="37"/>
+      <c r="AF1" s="37"/>
+      <c r="AG1" s="37"/>
+      <c r="AH1" s="37"/>
+      <c r="AI1" s="37"/>
+      <c r="AJ1" s="37"/>
+      <c r="AK1" s="37"/>
+      <c r="AL1" s="38"/>
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="33"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="39"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="40"/>
+      <c r="AC2" s="40"/>
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="41"/>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="41"/>
-      <c r="F3" s="41"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="41"/>
-      <c r="I3" s="41"/>
-      <c r="J3" s="41"/>
-      <c r="K3" s="41"/>
-      <c r="L3" s="41"/>
-      <c r="M3" s="41"/>
-      <c r="N3" s="41"/>
-      <c r="O3" s="41"/>
-      <c r="P3" s="41"/>
-      <c r="Q3" s="41"/>
-      <c r="R3" s="41"/>
-      <c r="S3" s="41"/>
-      <c r="T3" s="41"/>
-      <c r="U3" s="41"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="41"/>
-      <c r="X3" s="41"/>
-      <c r="Y3" s="41"/>
-      <c r="Z3" s="41"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="42"/>
-      <c r="AI3" s="44" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="51" t="s">
         <v>6</v>
       </c>
       <c r="AJ3" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="43" t="s">
+      <c r="AK3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="45" t="s">
+      <c r="AL3" s="52" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="35"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
@@ -2265,10 +2265,10 @@
       <c r="AF4" s="2"/>
       <c r="AG4" s="25"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="44"/>
+      <c r="AI4" s="51"/>
       <c r="AJ4" s="56"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="46"/>
+      <c r="AK4" s="51"/>
+      <c r="AL4" s="53"/>
     </row>
     <row r="5" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
@@ -3245,86 +3245,86 @@
       <c r="AL26" s="7"/>
     </row>
     <row r="27" spans="1:38" s="8" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="47" t="s">
+      <c r="A27" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="48"/>
-      <c r="S27" s="48"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="48"/>
-      <c r="V27" s="48"/>
-      <c r="W27" s="48"/>
-      <c r="X27" s="48"/>
-      <c r="Y27" s="48"/>
-      <c r="Z27" s="48"/>
-      <c r="AA27" s="48"/>
-      <c r="AB27" s="48"/>
-      <c r="AC27" s="48"/>
-      <c r="AD27" s="48"/>
-      <c r="AE27" s="48"/>
-      <c r="AF27" s="48"/>
-      <c r="AG27" s="48"/>
-      <c r="AH27" s="48"/>
-      <c r="AI27" s="48"/>
-      <c r="AJ27" s="48"/>
-      <c r="AK27" s="48"/>
-      <c r="AL27" s="49"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+      <c r="N27" s="28"/>
+      <c r="O27" s="28"/>
+      <c r="P27" s="28"/>
+      <c r="Q27" s="28"/>
+      <c r="R27" s="28"/>
+      <c r="S27" s="28"/>
+      <c r="T27" s="28"/>
+      <c r="U27" s="28"/>
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28"/>
+      <c r="Y27" s="28"/>
+      <c r="Z27" s="28"/>
+      <c r="AA27" s="28"/>
+      <c r="AB27" s="28"/>
+      <c r="AC27" s="28"/>
+      <c r="AD27" s="28"/>
+      <c r="AE27" s="28"/>
+      <c r="AF27" s="28"/>
+      <c r="AG27" s="28"/>
+      <c r="AH27" s="28"/>
+      <c r="AI27" s="28"/>
+      <c r="AJ27" s="28"/>
+      <c r="AK27" s="28"/>
+      <c r="AL27" s="29"/>
     </row>
     <row r="28" spans="1:38" s="8" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="50"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="51"/>
-      <c r="F28" s="51"/>
-      <c r="G28" s="51"/>
-      <c r="H28" s="51"/>
-      <c r="I28" s="51"/>
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="51"/>
-      <c r="M28" s="51"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="51"/>
-      <c r="S28" s="51"/>
-      <c r="T28" s="51"/>
-      <c r="U28" s="51"/>
-      <c r="V28" s="51"/>
-      <c r="W28" s="51"/>
-      <c r="X28" s="51"/>
-      <c r="Y28" s="51"/>
-      <c r="Z28" s="51"/>
-      <c r="AA28" s="51"/>
-      <c r="AB28" s="51"/>
-      <c r="AC28" s="51"/>
-      <c r="AD28" s="51"/>
-      <c r="AE28" s="51"/>
-      <c r="AF28" s="51"/>
-      <c r="AG28" s="51"/>
-      <c r="AH28" s="51"/>
-      <c r="AI28" s="51"/>
-      <c r="AJ28" s="51"/>
-      <c r="AK28" s="51"/>
-      <c r="AL28" s="52"/>
+      <c r="A28" s="30"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="32"/>
     </row>
     <row r="29" spans="1:38" s="12" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9" t="s">
@@ -3338,44 +3338,44 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="53" t="s">
+      <c r="H29" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="53"/>
-      <c r="J29" s="53"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
       <c r="O29" s="11"/>
-      <c r="P29" s="53" t="s">
+      <c r="P29" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="Q29" s="53"/>
-      <c r="R29" s="53"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
       <c r="S29" s="11"/>
       <c r="T29" s="11"/>
       <c r="U29" s="11"/>
-      <c r="V29" s="53" t="s">
+      <c r="V29" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="W29" s="53"/>
-      <c r="X29" s="53"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="33"/>
       <c r="Y29" s="11"/>
       <c r="Z29" s="11"/>
       <c r="AA29" s="11"/>
-      <c r="AB29" s="53" t="s">
+      <c r="AB29" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="AC29" s="53"/>
-      <c r="AD29" s="53"/>
+      <c r="AC29" s="33"/>
+      <c r="AD29" s="33"/>
       <c r="AE29" s="11"/>
       <c r="AF29" s="11"/>
       <c r="AG29" s="11"/>
-      <c r="AH29" s="57" t="s">
+      <c r="AH29" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="AI29" s="57"/>
+      <c r="AI29" s="54"/>
       <c r="AJ29" s="10"/>
       <c r="AK29" s="10"/>
       <c r="AL29" s="10"/>
@@ -3387,12 +3387,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A27:AL28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="AB29:AD29"/>
-    <mergeCell ref="AH29:AI29"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="X1:AL2"/>
     <mergeCell ref="A2:W2"/>
@@ -3404,6 +3398,12 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="A27:AL28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="AB29:AD29"/>
+    <mergeCell ref="AH29:AI29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/public/templates/drivebonus_template.xlsx
+++ b/public/templates/drivebonus_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\wordtoexcel\staff_manager\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A8B72E-3DBC-47F9-B1F9-B7D9204950A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E90D04-D626-4879-A95F-7C1B9974BBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{FE9DB102-5480-4C6F-9AE4-967FBD7E5687}"/>
   </bookViews>
@@ -330,7 +330,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -422,6 +422,19 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -855,6 +868,60 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="5"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -879,73 +946,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" indent="5"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1275,151 +1288,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="36" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="37"/>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="38"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="30"/>
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="40"/>
-      <c r="AK2" s="40"/>
-      <c r="AL2" s="41"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="33"/>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="48"/>
-      <c r="AA3" s="48"/>
-      <c r="AB3" s="48"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="48"/>
-      <c r="AF3" s="48"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="50" t="s">
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="40"/>
+      <c r="AI3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="AJ3" s="50" t="s">
+      <c r="AJ3" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="50" t="s">
+      <c r="AK3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="52" t="s">
+      <c r="AL3" s="43" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="43"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="57"/>
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1453,10 +1466,10 @@
       <c r="AF4" s="2"/>
       <c r="AG4" s="2"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="51"/>
-      <c r="AJ4" s="51"/>
-      <c r="AK4" s="51"/>
-      <c r="AL4" s="53"/>
+      <c r="AI4" s="42"/>
+      <c r="AJ4" s="42"/>
+      <c r="AK4" s="42"/>
+      <c r="AL4" s="44"/>
     </row>
     <row r="5" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="26" t="s">
@@ -1905,86 +1918,86 @@
       <c r="AL14" s="7"/>
     </row>
     <row r="15" spans="1:38" s="8" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="28"/>
-      <c r="O15" s="28"/>
-      <c r="P15" s="28"/>
-      <c r="Q15" s="28"/>
-      <c r="R15" s="28"/>
-      <c r="S15" s="28"/>
-      <c r="T15" s="28"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="28"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="28"/>
-      <c r="AB15" s="28"/>
-      <c r="AC15" s="28"/>
-      <c r="AD15" s="28"/>
-      <c r="AE15" s="28"/>
-      <c r="AF15" s="28"/>
-      <c r="AG15" s="28"/>
-      <c r="AH15" s="28"/>
-      <c r="AI15" s="28"/>
-      <c r="AJ15" s="28"/>
-      <c r="AK15" s="28"/>
-      <c r="AL15" s="29"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
+      <c r="S15" s="46"/>
+      <c r="T15" s="46"/>
+      <c r="U15" s="46"/>
+      <c r="V15" s="46"/>
+      <c r="W15" s="46"/>
+      <c r="X15" s="46"/>
+      <c r="Y15" s="46"/>
+      <c r="Z15" s="46"/>
+      <c r="AA15" s="46"/>
+      <c r="AB15" s="46"/>
+      <c r="AC15" s="46"/>
+      <c r="AD15" s="46"/>
+      <c r="AE15" s="46"/>
+      <c r="AF15" s="46"/>
+      <c r="AG15" s="46"/>
+      <c r="AH15" s="46"/>
+      <c r="AI15" s="46"/>
+      <c r="AJ15" s="46"/>
+      <c r="AK15" s="46"/>
+      <c r="AL15" s="47"/>
     </row>
     <row r="16" spans="1:38" s="8" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="30"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="31"/>
-      <c r="Q16" s="31"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="31"/>
-      <c r="T16" s="31"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="31"/>
-      <c r="Z16" s="31"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="31"/>
-      <c r="AC16" s="31"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="31"/>
-      <c r="AF16" s="31"/>
-      <c r="AG16" s="31"/>
-      <c r="AH16" s="31"/>
-      <c r="AI16" s="31"/>
-      <c r="AJ16" s="31"/>
-      <c r="AK16" s="31"/>
-      <c r="AL16" s="32"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+      <c r="N16" s="49"/>
+      <c r="O16" s="49"/>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="49"/>
+      <c r="R16" s="49"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+      <c r="Y16" s="49"/>
+      <c r="Z16" s="49"/>
+      <c r="AA16" s="49"/>
+      <c r="AB16" s="49"/>
+      <c r="AC16" s="49"/>
+      <c r="AD16" s="49"/>
+      <c r="AE16" s="49"/>
+      <c r="AF16" s="49"/>
+      <c r="AG16" s="49"/>
+      <c r="AH16" s="49"/>
+      <c r="AI16" s="49"/>
+      <c r="AJ16" s="49"/>
+      <c r="AK16" s="49"/>
+      <c r="AL16" s="50"/>
     </row>
     <row r="17" spans="1:38" s="12" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="9" t="s">
@@ -1998,50 +2011,56 @@
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="33" t="s">
+      <c r="H17" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
+      <c r="I17" s="51"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="33" t="s">
+      <c r="P17" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
+      <c r="Q17" s="51"/>
+      <c r="R17" s="51"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
-      <c r="V17" s="33" t="s">
+      <c r="V17" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="W17" s="33"/>
-      <c r="X17" s="33"/>
+      <c r="W17" s="51"/>
+      <c r="X17" s="51"/>
       <c r="Y17" s="11"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
-      <c r="AB17" s="33" t="s">
+      <c r="AB17" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="33"/>
+      <c r="AC17" s="51"/>
+      <c r="AD17" s="51"/>
       <c r="AE17" s="11"/>
       <c r="AF17" s="11"/>
       <c r="AG17" s="11"/>
-      <c r="AH17" s="33" t="s">
+      <c r="AH17" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="AI17" s="34"/>
+      <c r="AI17" s="52"/>
       <c r="AJ17" s="10"/>
       <c r="AK17" s="10"/>
       <c r="AL17" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A15:AL16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="AB17:AD17"/>
+    <mergeCell ref="AH17:AI17"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="X1:AL2"/>
     <mergeCell ref="A2:W2"/>
@@ -2053,12 +2072,6 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="A15:AL16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="AB17:AD17"/>
-    <mergeCell ref="AH17:AI17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2087,151 +2100,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
-      <c r="J1" s="35"/>
-      <c r="K1" s="35"/>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="36" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="27"/>
+      <c r="V1" s="27"/>
+      <c r="W1" s="27"/>
+      <c r="X1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="37"/>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="38"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
+      <c r="AD1" s="29"/>
+      <c r="AE1" s="29"/>
+      <c r="AF1" s="29"/>
+      <c r="AG1" s="29"/>
+      <c r="AH1" s="29"/>
+      <c r="AI1" s="29"/>
+      <c r="AJ1" s="29"/>
+      <c r="AK1" s="29"/>
+      <c r="AL1" s="30"/>
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="40"/>
-      <c r="AC2" s="40"/>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="40"/>
-      <c r="AH2" s="40"/>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="40"/>
-      <c r="AK2" s="40"/>
-      <c r="AL2" s="41"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="27"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="31"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="33"/>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="47" t="s">
+      <c r="D3" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="48"/>
-      <c r="Y3" s="48"/>
-      <c r="Z3" s="48"/>
-      <c r="AA3" s="48"/>
-      <c r="AB3" s="48"/>
-      <c r="AC3" s="48"/>
-      <c r="AD3" s="48"/>
-      <c r="AE3" s="48"/>
-      <c r="AF3" s="48"/>
-      <c r="AG3" s="48"/>
-      <c r="AH3" s="49"/>
-      <c r="AI3" s="51" t="s">
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="39"/>
+      <c r="W3" s="39"/>
+      <c r="X3" s="39"/>
+      <c r="Y3" s="39"/>
+      <c r="Z3" s="39"/>
+      <c r="AA3" s="39"/>
+      <c r="AB3" s="39"/>
+      <c r="AC3" s="39"/>
+      <c r="AD3" s="39"/>
+      <c r="AE3" s="39"/>
+      <c r="AF3" s="39"/>
+      <c r="AG3" s="39"/>
+      <c r="AH3" s="40"/>
+      <c r="AI3" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="AJ3" s="55" t="s">
+      <c r="AJ3" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="50" t="s">
+      <c r="AK3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="52" t="s">
+      <c r="AL3" s="43" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="43"/>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
@@ -2265,10 +2278,10 @@
       <c r="AF4" s="2"/>
       <c r="AG4" s="25"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="51"/>
-      <c r="AJ4" s="56"/>
-      <c r="AK4" s="51"/>
-      <c r="AL4" s="53"/>
+      <c r="AI4" s="42"/>
+      <c r="AJ4" s="54"/>
+      <c r="AK4" s="42"/>
+      <c r="AL4" s="44"/>
     </row>
     <row r="5" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
@@ -3245,86 +3258,86 @@
       <c r="AL26" s="7"/>
     </row>
     <row r="27" spans="1:38" s="8" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="27" t="s">
+      <c r="A27" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-      <c r="N27" s="28"/>
-      <c r="O27" s="28"/>
-      <c r="P27" s="28"/>
-      <c r="Q27" s="28"/>
-      <c r="R27" s="28"/>
-      <c r="S27" s="28"/>
-      <c r="T27" s="28"/>
-      <c r="U27" s="28"/>
-      <c r="V27" s="28"/>
-      <c r="W27" s="28"/>
-      <c r="X27" s="28"/>
-      <c r="Y27" s="28"/>
-      <c r="Z27" s="28"/>
-      <c r="AA27" s="28"/>
-      <c r="AB27" s="28"/>
-      <c r="AC27" s="28"/>
-      <c r="AD27" s="28"/>
-      <c r="AE27" s="28"/>
-      <c r="AF27" s="28"/>
-      <c r="AG27" s="28"/>
-      <c r="AH27" s="28"/>
-      <c r="AI27" s="28"/>
-      <c r="AJ27" s="28"/>
-      <c r="AK27" s="28"/>
-      <c r="AL27" s="29"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="46"/>
+      <c r="D27" s="46"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="46"/>
+      <c r="G27" s="46"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="46"/>
+      <c r="L27" s="46"/>
+      <c r="M27" s="46"/>
+      <c r="N27" s="46"/>
+      <c r="O27" s="46"/>
+      <c r="P27" s="46"/>
+      <c r="Q27" s="46"/>
+      <c r="R27" s="46"/>
+      <c r="S27" s="46"/>
+      <c r="T27" s="46"/>
+      <c r="U27" s="46"/>
+      <c r="V27" s="46"/>
+      <c r="W27" s="46"/>
+      <c r="X27" s="46"/>
+      <c r="Y27" s="46"/>
+      <c r="Z27" s="46"/>
+      <c r="AA27" s="46"/>
+      <c r="AB27" s="46"/>
+      <c r="AC27" s="46"/>
+      <c r="AD27" s="46"/>
+      <c r="AE27" s="46"/>
+      <c r="AF27" s="46"/>
+      <c r="AG27" s="46"/>
+      <c r="AH27" s="46"/>
+      <c r="AI27" s="46"/>
+      <c r="AJ27" s="46"/>
+      <c r="AK27" s="46"/>
+      <c r="AL27" s="47"/>
     </row>
     <row r="28" spans="1:38" s="8" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="30"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="31"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="31"/>
-      <c r="AF28" s="31"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="31"/>
-      <c r="AI28" s="31"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="31"/>
-      <c r="AL28" s="32"/>
+      <c r="A28" s="48"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="49"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="49"/>
+      <c r="AB28" s="49"/>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="49"/>
+      <c r="AE28" s="49"/>
+      <c r="AF28" s="49"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="50"/>
     </row>
     <row r="29" spans="1:38" s="12" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9" t="s">
@@ -3338,44 +3351,44 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="33" t="s">
+      <c r="H29" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="51"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
       <c r="O29" s="11"/>
-      <c r="P29" s="33" t="s">
+      <c r="P29" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="Q29" s="33"/>
-      <c r="R29" s="33"/>
+      <c r="Q29" s="51"/>
+      <c r="R29" s="51"/>
       <c r="S29" s="11"/>
       <c r="T29" s="11"/>
       <c r="U29" s="11"/>
-      <c r="V29" s="33" t="s">
+      <c r="V29" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="W29" s="33"/>
-      <c r="X29" s="33"/>
+      <c r="W29" s="51"/>
+      <c r="X29" s="51"/>
       <c r="Y29" s="11"/>
       <c r="Z29" s="11"/>
       <c r="AA29" s="11"/>
-      <c r="AB29" s="33" t="s">
+      <c r="AB29" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="AC29" s="33"/>
-      <c r="AD29" s="33"/>
+      <c r="AC29" s="51"/>
+      <c r="AD29" s="51"/>
       <c r="AE29" s="11"/>
       <c r="AF29" s="11"/>
       <c r="AG29" s="11"/>
-      <c r="AH29" s="54" t="s">
+      <c r="AH29" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="AI29" s="54"/>
+      <c r="AI29" s="55"/>
       <c r="AJ29" s="10"/>
       <c r="AK29" s="10"/>
       <c r="AL29" s="10"/>
@@ -3387,6 +3400,12 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A27:AL28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="AB29:AD29"/>
+    <mergeCell ref="AH29:AI29"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="X1:AL2"/>
     <mergeCell ref="A2:W2"/>
@@ -3398,12 +3417,6 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
-    <mergeCell ref="A27:AL28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="AB29:AD29"/>
-    <mergeCell ref="AH29:AI29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/public/templates/drivebonus_template.xlsx
+++ b/public/templates/drivebonus_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\wordtoexcel\staff_manager\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E90D04-D626-4879-A95F-7C1B9974BBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77722F0F-CF82-461D-A762-91762FCF7346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{FE9DB102-5480-4C6F-9AE4-967FBD7E5687}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FE9DB102-5480-4C6F-9AE4-967FBD7E5687}"/>
   </bookViews>
   <sheets>
     <sheet name="正駕" sheetId="1" r:id="rId1"/>
@@ -49,9 +49,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -800,7 +797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -856,9 +853,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -868,6 +862,30 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -901,6 +919,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="distributed" vertical="center" indent="5"/>
     </xf>
@@ -922,43 +946,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1288,151 +1282,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="28" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="30"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="37"/>
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="39"/>
+      <c r="Z2" s="39"/>
+      <c r="AA2" s="39"/>
+      <c r="AB2" s="39"/>
+      <c r="AC2" s="39"/>
+      <c r="AD2" s="39"/>
+      <c r="AE2" s="39"/>
+      <c r="AF2" s="39"/>
+      <c r="AG2" s="39"/>
+      <c r="AH2" s="39"/>
+      <c r="AI2" s="39"/>
+      <c r="AJ2" s="39"/>
+      <c r="AK2" s="39"/>
+      <c r="AL2" s="40"/>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="41" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="AJ3" s="41" t="s">
+      <c r="AJ3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="41" t="s">
+      <c r="AK3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="43" t="s">
+      <c r="AL3" s="52" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="35"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="57"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
@@ -1466,13 +1460,13 @@
       <c r="AF4" s="2"/>
       <c r="AG4" s="2"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="42"/>
-      <c r="AJ4" s="42"/>
-      <c r="AK4" s="42"/>
-      <c r="AL4" s="44"/>
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="51"/>
+      <c r="AK4" s="51"/>
+      <c r="AL4" s="53"/>
     </row>
     <row r="5" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="25" t="s">
         <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1522,7 +1516,7 @@
       <c r="AL5" s="7"/>
     </row>
     <row r="6" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="26"/>
+      <c r="A6" s="25"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="6"/>
@@ -1566,7 +1560,7 @@
       <c r="AL6" s="7"/>
     </row>
     <row r="7" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="26"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
       <c r="D7" s="6"/>
@@ -1610,7 +1604,7 @@
       <c r="AL7" s="7"/>
     </row>
     <row r="8" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="26"/>
+      <c r="A8" s="25"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
       <c r="D8" s="6"/>
@@ -1654,7 +1648,7 @@
       <c r="AL8" s="7"/>
     </row>
     <row r="9" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="26"/>
+      <c r="A9" s="25"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="6"/>
@@ -1698,7 +1692,7 @@
       <c r="AL9" s="7"/>
     </row>
     <row r="10" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="26"/>
+      <c r="A10" s="25"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="6"/>
@@ -1742,7 +1736,7 @@
       <c r="AL10" s="7"/>
     </row>
     <row r="11" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="26"/>
+      <c r="A11" s="25"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="6"/>
@@ -1786,7 +1780,7 @@
       <c r="AL11" s="7"/>
     </row>
     <row r="12" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="26"/>
+      <c r="A12" s="25"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="6"/>
@@ -1830,7 +1824,7 @@
       <c r="AL12" s="7"/>
     </row>
     <row r="13" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="26"/>
+      <c r="A13" s="25"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="6"/>
@@ -1874,7 +1868,7 @@
       <c r="AL13" s="7"/>
     </row>
     <row r="14" spans="1:38" ht="69.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="26"/>
+      <c r="A14" s="25"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="6"/>
@@ -1918,86 +1912,86 @@
       <c r="AL14" s="7"/>
     </row>
     <row r="15" spans="1:38" s="8" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46"/>
-      <c r="O15" s="46"/>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="46"/>
-      <c r="Y15" s="46"/>
-      <c r="Z15" s="46"/>
-      <c r="AA15" s="46"/>
-      <c r="AB15" s="46"/>
-      <c r="AC15" s="46"/>
-      <c r="AD15" s="46"/>
-      <c r="AE15" s="46"/>
-      <c r="AF15" s="46"/>
-      <c r="AG15" s="46"/>
-      <c r="AH15" s="46"/>
-      <c r="AI15" s="46"/>
-      <c r="AJ15" s="46"/>
-      <c r="AK15" s="46"/>
-      <c r="AL15" s="47"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="27"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="27"/>
+      <c r="O15" s="27"/>
+      <c r="P15" s="27"/>
+      <c r="Q15" s="27"/>
+      <c r="R15" s="27"/>
+      <c r="S15" s="27"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27"/>
+      <c r="AB15" s="27"/>
+      <c r="AC15" s="27"/>
+      <c r="AD15" s="27"/>
+      <c r="AE15" s="27"/>
+      <c r="AF15" s="27"/>
+      <c r="AG15" s="27"/>
+      <c r="AH15" s="27"/>
+      <c r="AI15" s="27"/>
+      <c r="AJ15" s="27"/>
+      <c r="AK15" s="27"/>
+      <c r="AL15" s="28"/>
     </row>
     <row r="16" spans="1:38" s="8" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="48"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="49"/>
-      <c r="L16" s="49"/>
-      <c r="M16" s="49"/>
-      <c r="N16" s="49"/>
-      <c r="O16" s="49"/>
-      <c r="P16" s="49"/>
-      <c r="Q16" s="49"/>
-      <c r="R16" s="49"/>
-      <c r="S16" s="49"/>
-      <c r="T16" s="49"/>
-      <c r="U16" s="49"/>
-      <c r="V16" s="49"/>
-      <c r="W16" s="49"/>
-      <c r="X16" s="49"/>
-      <c r="Y16" s="49"/>
-      <c r="Z16" s="49"/>
-      <c r="AA16" s="49"/>
-      <c r="AB16" s="49"/>
-      <c r="AC16" s="49"/>
-      <c r="AD16" s="49"/>
-      <c r="AE16" s="49"/>
-      <c r="AF16" s="49"/>
-      <c r="AG16" s="49"/>
-      <c r="AH16" s="49"/>
-      <c r="AI16" s="49"/>
-      <c r="AJ16" s="49"/>
-      <c r="AK16" s="49"/>
-      <c r="AL16" s="50"/>
+      <c r="A16" s="29"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="30"/>
+      <c r="X16" s="30"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="30"/>
+      <c r="AA16" s="30"/>
+      <c r="AB16" s="30"/>
+      <c r="AC16" s="30"/>
+      <c r="AD16" s="30"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="30"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="30"/>
+      <c r="AJ16" s="30"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="31"/>
     </row>
     <row r="17" spans="1:38" s="12" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="9" t="s">
@@ -2011,56 +2005,50 @@
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="51" t="s">
+      <c r="H17" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="51"/>
-      <c r="J17" s="51"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
       <c r="M17" s="11"/>
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
-      <c r="P17" s="51" t="s">
+      <c r="P17" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="51"/>
+      <c r="Q17" s="32"/>
+      <c r="R17" s="32"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>
       <c r="U17" s="11"/>
-      <c r="V17" s="51" t="s">
+      <c r="V17" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="W17" s="51"/>
-      <c r="X17" s="51"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="32"/>
       <c r="Y17" s="11"/>
       <c r="Z17" s="11"/>
       <c r="AA17" s="11"/>
-      <c r="AB17" s="51" t="s">
+      <c r="AB17" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="AC17" s="51"/>
-      <c r="AD17" s="51"/>
+      <c r="AC17" s="32"/>
+      <c r="AD17" s="32"/>
       <c r="AE17" s="11"/>
       <c r="AF17" s="11"/>
       <c r="AG17" s="11"/>
-      <c r="AH17" s="51" t="s">
+      <c r="AH17" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="AI17" s="52"/>
+      <c r="AI17" s="33"/>
       <c r="AJ17" s="10"/>
       <c r="AK17" s="10"/>
       <c r="AL17" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A15:AL16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="P17:R17"/>
-    <mergeCell ref="V17:X17"/>
-    <mergeCell ref="AB17:AD17"/>
-    <mergeCell ref="AH17:AI17"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="X1:AL2"/>
     <mergeCell ref="A2:W2"/>
@@ -2072,6 +2060,12 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="A15:AL16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="P17:R17"/>
+    <mergeCell ref="V17:X17"/>
+    <mergeCell ref="AB17:AD17"/>
+    <mergeCell ref="AH17:AI17"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2100,151 +2094,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:38" ht="44.45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
-      <c r="P1" s="27"/>
-      <c r="Q1" s="27"/>
-      <c r="R1" s="27"/>
-      <c r="S1" s="27"/>
-      <c r="T1" s="27"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="27"/>
-      <c r="W1" s="27"/>
-      <c r="X1" s="28" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-      <c r="AA1" s="29"/>
-      <c r="AB1" s="29"/>
-      <c r="AC1" s="29"/>
-      <c r="AD1" s="29"/>
-      <c r="AE1" s="29"/>
-      <c r="AF1" s="29"/>
-      <c r="AG1" s="29"/>
-      <c r="AH1" s="29"/>
-      <c r="AI1" s="29"/>
-      <c r="AJ1" s="29"/>
-      <c r="AK1" s="29"/>
-      <c r="AL1" s="30"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="36"/>
+      <c r="AH1" s="36"/>
+      <c r="AI1" s="36"/>
+      <c r="AJ1" s="36"/>
+      <c r="AK1" s="36"/>
+      <c r="AL1" s="37"/>
     </row>
     <row r="2" spans="1:38" ht="50.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="31"/>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="32"/>
-      <c r="AA2" s="32"/>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="32"/>
-      <c r="AG2" s="32"/>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="32"/>
-      <c r="AJ2" s="32"/>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="39"/>
+      <c r="Z2" s="39"/>
+      <c r="AA2" s="39"/>
+      <c r="AB2" s="39"/>
+      <c r="AC2" s="39"/>
+      <c r="AD2" s="39"/>
+      <c r="AE2" s="39"/>
+      <c r="AF2" s="39"/>
+      <c r="AG2" s="39"/>
+      <c r="AH2" s="39"/>
+      <c r="AI2" s="39"/>
+      <c r="AJ2" s="39"/>
+      <c r="AK2" s="39"/>
+      <c r="AL2" s="40"/>
     </row>
     <row r="3" spans="1:38" s="1" customFormat="1" ht="42.95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="36" t="s">
+      <c r="C3" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
-      <c r="P3" s="39"/>
-      <c r="Q3" s="39"/>
-      <c r="R3" s="39"/>
-      <c r="S3" s="39"/>
-      <c r="T3" s="39"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="39"/>
-      <c r="W3" s="39"/>
-      <c r="X3" s="39"/>
-      <c r="Y3" s="39"/>
-      <c r="Z3" s="39"/>
-      <c r="AA3" s="39"/>
-      <c r="AB3" s="39"/>
-      <c r="AC3" s="39"/>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="39"/>
-      <c r="AG3" s="39"/>
-      <c r="AH3" s="40"/>
-      <c r="AI3" s="42" t="s">
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="48"/>
+      <c r="X3" s="48"/>
+      <c r="Y3" s="48"/>
+      <c r="Z3" s="48"/>
+      <c r="AA3" s="48"/>
+      <c r="AB3" s="48"/>
+      <c r="AC3" s="48"/>
+      <c r="AD3" s="48"/>
+      <c r="AE3" s="48"/>
+      <c r="AF3" s="48"/>
+      <c r="AG3" s="48"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="AJ3" s="53" t="s">
+      <c r="AJ3" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="AK3" s="41" t="s">
+      <c r="AK3" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="AL3" s="43" t="s">
+      <c r="AL3" s="52" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:38" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="35"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
       <c r="D4" s="2" t="s">
         <v>22</v>
       </c>
@@ -2276,12 +2270,12 @@
       <c r="AD4" s="2"/>
       <c r="AE4" s="2"/>
       <c r="AF4" s="2"/>
-      <c r="AG4" s="25"/>
+      <c r="AG4" s="24"/>
       <c r="AH4" s="2"/>
-      <c r="AI4" s="42"/>
-      <c r="AJ4" s="54"/>
-      <c r="AK4" s="42"/>
-      <c r="AL4" s="44"/>
+      <c r="AI4" s="51"/>
+      <c r="AJ4" s="56"/>
+      <c r="AK4" s="51"/>
+      <c r="AL4" s="53"/>
     </row>
     <row r="5" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
@@ -2293,37 +2287,37 @@
       <c r="C5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
-      <c r="P5" s="24"/>
-      <c r="Q5" s="24"/>
-      <c r="R5" s="24"/>
-      <c r="S5" s="24"/>
-      <c r="T5" s="24"/>
-      <c r="U5" s="24"/>
-      <c r="V5" s="24"/>
-      <c r="W5" s="24"/>
-      <c r="X5" s="24"/>
-      <c r="Y5" s="24"/>
-      <c r="Z5" s="24"/>
-      <c r="AA5" s="24"/>
-      <c r="AB5" s="24"/>
-      <c r="AC5" s="24"/>
-      <c r="AD5" s="24"/>
-      <c r="AE5" s="24"/>
-      <c r="AF5" s="24"/>
-      <c r="AG5" s="24"/>
-      <c r="AH5" s="24"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
+      <c r="U5" s="23"/>
+      <c r="V5" s="23"/>
+      <c r="W5" s="23"/>
+      <c r="X5" s="23"/>
+      <c r="Y5" s="23"/>
+      <c r="Z5" s="23"/>
+      <c r="AA5" s="23"/>
+      <c r="AB5" s="23"/>
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="23"/>
+      <c r="AF5" s="23"/>
+      <c r="AG5" s="23"/>
+      <c r="AH5" s="23"/>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="19" t="s">
         <v>10</v>
@@ -2336,38 +2330,38 @@
     <row r="6" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="17"/>
       <c r="B6" s="16"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="24"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="24"/>
-      <c r="M6" s="24"/>
-      <c r="N6" s="24"/>
-      <c r="O6" s="24"/>
-      <c r="P6" s="24"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="24"/>
-      <c r="S6" s="24"/>
-      <c r="T6" s="24"/>
-      <c r="U6" s="24"/>
-      <c r="V6" s="24"/>
-      <c r="W6" s="24"/>
-      <c r="X6" s="24"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="23"/>
+      <c r="U6" s="23"/>
+      <c r="V6" s="23"/>
+      <c r="W6" s="23"/>
+      <c r="X6" s="23"/>
       <c r="Y6" s="21"/>
       <c r="Z6" s="21"/>
-      <c r="AA6" s="24"/>
-      <c r="AB6" s="24"/>
-      <c r="AC6" s="24"/>
-      <c r="AD6" s="24"/>
-      <c r="AE6" s="24"/>
-      <c r="AF6" s="24"/>
-      <c r="AG6" s="24"/>
-      <c r="AH6" s="24"/>
+      <c r="AA6" s="23"/>
+      <c r="AB6" s="23"/>
+      <c r="AC6" s="23"/>
+      <c r="AD6" s="23"/>
+      <c r="AE6" s="23"/>
+      <c r="AF6" s="23"/>
+      <c r="AG6" s="23"/>
+      <c r="AH6" s="23"/>
       <c r="AI6" s="22"/>
       <c r="AJ6" s="19" t="s">
         <v>10</v>
@@ -2380,38 +2374,38 @@
     <row r="7" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="17"/>
       <c r="B7" s="16"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="24"/>
-      <c r="M7" s="24"/>
-      <c r="N7" s="24"/>
-      <c r="O7" s="24"/>
-      <c r="P7" s="24"/>
-      <c r="Q7" s="24"/>
-      <c r="R7" s="24"/>
-      <c r="S7" s="24"/>
-      <c r="T7" s="24"/>
-      <c r="U7" s="24"/>
-      <c r="V7" s="24"/>
-      <c r="W7" s="24"/>
-      <c r="X7" s="24"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="23"/>
+      <c r="Q7" s="23"/>
+      <c r="R7" s="23"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="23"/>
+      <c r="U7" s="23"/>
+      <c r="V7" s="23"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="23"/>
       <c r="Y7" s="21"/>
       <c r="Z7" s="21"/>
-      <c r="AA7" s="24"/>
-      <c r="AB7" s="24"/>
-      <c r="AC7" s="24"/>
-      <c r="AD7" s="24"/>
-      <c r="AE7" s="24"/>
-      <c r="AF7" s="24"/>
-      <c r="AG7" s="24"/>
-      <c r="AH7" s="24"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="23"/>
+      <c r="AD7" s="23"/>
+      <c r="AE7" s="23"/>
+      <c r="AF7" s="23"/>
+      <c r="AG7" s="23"/>
+      <c r="AH7" s="23"/>
       <c r="AI7" s="22"/>
       <c r="AJ7" s="19" t="s">
         <v>10</v>
@@ -2424,38 +2418,38 @@
     <row r="8" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17"/>
       <c r="B8" s="16"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="24"/>
-      <c r="G8" s="24"/>
-      <c r="H8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="24"/>
-      <c r="K8" s="24"/>
-      <c r="L8" s="24"/>
-      <c r="M8" s="24"/>
-      <c r="N8" s="24"/>
-      <c r="O8" s="24"/>
-      <c r="P8" s="24"/>
-      <c r="Q8" s="24"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
-      <c r="W8" s="24"/>
-      <c r="X8" s="24"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
+      <c r="F8" s="23"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="23"/>
+      <c r="M8" s="23"/>
+      <c r="N8" s="23"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="23"/>
+      <c r="Q8" s="23"/>
+      <c r="R8" s="23"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="23"/>
+      <c r="U8" s="23"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="23"/>
       <c r="Y8" s="21"/>
       <c r="Z8" s="21"/>
-      <c r="AA8" s="24"/>
-      <c r="AB8" s="24"/>
-      <c r="AC8" s="24"/>
-      <c r="AD8" s="24"/>
-      <c r="AE8" s="24"/>
-      <c r="AF8" s="24"/>
-      <c r="AG8" s="24"/>
-      <c r="AH8" s="24"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="23"/>
+      <c r="AC8" s="23"/>
+      <c r="AD8" s="23"/>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="23"/>
+      <c r="AG8" s="23"/>
+      <c r="AH8" s="23"/>
       <c r="AI8" s="22"/>
       <c r="AJ8" s="19" t="s">
         <v>10</v>
@@ -2468,38 +2462,38 @@
     <row r="9" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="17"/>
       <c r="B9" s="16"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="24"/>
-      <c r="O9" s="24"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="24"/>
-      <c r="R9" s="24"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="24"/>
-      <c r="U9" s="24"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="24"/>
-      <c r="X9" s="24"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="23"/>
+      <c r="M9" s="23"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="23"/>
+      <c r="Q9" s="23"/>
+      <c r="R9" s="23"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="23"/>
+      <c r="V9" s="23"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="23"/>
       <c r="Y9" s="21"/>
       <c r="Z9" s="21"/>
-      <c r="AA9" s="24"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="24"/>
-      <c r="AD9" s="24"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="24"/>
-      <c r="AH9" s="24"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="23"/>
+      <c r="AC9" s="23"/>
+      <c r="AD9" s="23"/>
+      <c r="AE9" s="23"/>
+      <c r="AF9" s="23"/>
+      <c r="AG9" s="23"/>
+      <c r="AH9" s="23"/>
       <c r="AI9" s="22"/>
       <c r="AJ9" s="19" t="s">
         <v>10</v>
@@ -2512,38 +2506,38 @@
     <row r="10" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="17"/>
       <c r="B10" s="16"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="24"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="24"/>
-      <c r="N10" s="24"/>
-      <c r="O10" s="24"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="24"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="U10" s="24"/>
-      <c r="V10" s="24"/>
-      <c r="W10" s="24"/>
-      <c r="X10" s="24"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="23"/>
+      <c r="M10" s="23"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="23"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="23"/>
+      <c r="V10" s="23"/>
+      <c r="W10" s="23"/>
+      <c r="X10" s="23"/>
       <c r="Y10" s="21"/>
       <c r="Z10" s="21"/>
-      <c r="AA10" s="24"/>
-      <c r="AB10" s="24"/>
-      <c r="AC10" s="24"/>
-      <c r="AD10" s="24"/>
-      <c r="AE10" s="24"/>
-      <c r="AF10" s="24"/>
-      <c r="AG10" s="24"/>
-      <c r="AH10" s="24"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="23"/>
+      <c r="AC10" s="23"/>
+      <c r="AD10" s="23"/>
+      <c r="AE10" s="23"/>
+      <c r="AF10" s="23"/>
+      <c r="AG10" s="23"/>
+      <c r="AH10" s="23"/>
       <c r="AI10" s="22"/>
       <c r="AJ10" s="19" t="s">
         <v>10</v>
@@ -2556,38 +2550,38 @@
     <row r="11" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17"/>
       <c r="B11" s="16"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" s="24"/>
-      <c r="O11" s="24"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="24"/>
-      <c r="R11" s="24"/>
-      <c r="S11" s="24"/>
-      <c r="T11" s="24"/>
-      <c r="U11" s="24"/>
-      <c r="V11" s="24"/>
-      <c r="W11" s="24"/>
-      <c r="X11" s="24"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="23"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+      <c r="O11" s="23"/>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="23"/>
+      <c r="S11" s="23"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="23"/>
+      <c r="V11" s="23"/>
+      <c r="W11" s="23"/>
+      <c r="X11" s="23"/>
       <c r="Y11" s="21"/>
       <c r="Z11" s="21"/>
-      <c r="AA11" s="24"/>
-      <c r="AB11" s="24"/>
-      <c r="AC11" s="24"/>
-      <c r="AD11" s="24"/>
-      <c r="AE11" s="24"/>
-      <c r="AF11" s="24"/>
-      <c r="AG11" s="24"/>
-      <c r="AH11" s="24"/>
+      <c r="AA11" s="23"/>
+      <c r="AB11" s="23"/>
+      <c r="AC11" s="23"/>
+      <c r="AD11" s="23"/>
+      <c r="AE11" s="23"/>
+      <c r="AF11" s="23"/>
+      <c r="AG11" s="23"/>
+      <c r="AH11" s="23"/>
       <c r="AI11" s="22"/>
       <c r="AJ11" s="19" t="s">
         <v>10</v>
@@ -2600,38 +2594,38 @@
     <row r="12" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="17"/>
       <c r="B12" s="16"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
-      <c r="N12" s="24"/>
-      <c r="O12" s="24"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="24"/>
-      <c r="R12" s="24"/>
-      <c r="S12" s="24"/>
-      <c r="T12" s="24"/>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="24"/>
-      <c r="X12" s="24"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="23"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+      <c r="O12" s="23"/>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="23"/>
+      <c r="S12" s="23"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="23"/>
+      <c r="V12" s="23"/>
+      <c r="W12" s="23"/>
+      <c r="X12" s="23"/>
       <c r="Y12" s="21"/>
       <c r="Z12" s="21"/>
-      <c r="AA12" s="24"/>
-      <c r="AB12" s="24"/>
-      <c r="AC12" s="24"/>
-      <c r="AD12" s="24"/>
-      <c r="AE12" s="24"/>
-      <c r="AF12" s="24"/>
-      <c r="AG12" s="24"/>
-      <c r="AH12" s="24"/>
+      <c r="AA12" s="23"/>
+      <c r="AB12" s="23"/>
+      <c r="AC12" s="23"/>
+      <c r="AD12" s="23"/>
+      <c r="AE12" s="23"/>
+      <c r="AF12" s="23"/>
+      <c r="AG12" s="23"/>
+      <c r="AH12" s="23"/>
       <c r="AI12" s="22"/>
       <c r="AJ12" s="19" t="s">
         <v>10</v>
@@ -2644,38 +2638,38 @@
     <row r="13" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="17"/>
       <c r="B13" s="16"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" s="24"/>
-      <c r="O13" s="24"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="24"/>
-      <c r="R13" s="24"/>
-      <c r="S13" s="24"/>
-      <c r="T13" s="24"/>
-      <c r="U13" s="24"/>
-      <c r="V13" s="24"/>
-      <c r="W13" s="24"/>
-      <c r="X13" s="24"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="23"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+      <c r="O13" s="23"/>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="23"/>
+      <c r="S13" s="23"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="23"/>
+      <c r="V13" s="23"/>
+      <c r="W13" s="23"/>
+      <c r="X13" s="23"/>
       <c r="Y13" s="21"/>
       <c r="Z13" s="21"/>
-      <c r="AA13" s="24"/>
-      <c r="AB13" s="24"/>
-      <c r="AC13" s="24"/>
-      <c r="AD13" s="24"/>
-      <c r="AE13" s="24"/>
-      <c r="AF13" s="24"/>
-      <c r="AG13" s="24"/>
-      <c r="AH13" s="24"/>
+      <c r="AA13" s="23"/>
+      <c r="AB13" s="23"/>
+      <c r="AC13" s="23"/>
+      <c r="AD13" s="23"/>
+      <c r="AE13" s="23"/>
+      <c r="AF13" s="23"/>
+      <c r="AG13" s="23"/>
+      <c r="AH13" s="23"/>
       <c r="AI13" s="22"/>
       <c r="AJ13" s="19" t="s">
         <v>10</v>
@@ -2688,38 +2682,38 @@
     <row r="14" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="17"/>
       <c r="B14" s="16"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="24"/>
-      <c r="M14" s="24"/>
-      <c r="N14" s="24"/>
-      <c r="O14" s="24"/>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="24"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
-      <c r="V14" s="24"/>
-      <c r="W14" s="24"/>
-      <c r="X14" s="24"/>
+      <c r="C14" s="16"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+      <c r="O14" s="23"/>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="23"/>
+      <c r="S14" s="23"/>
+      <c r="T14" s="23"/>
+      <c r="U14" s="23"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
       <c r="Y14" s="21"/>
       <c r="Z14" s="21"/>
-      <c r="AA14" s="24"/>
-      <c r="AB14" s="24"/>
-      <c r="AC14" s="24"/>
-      <c r="AD14" s="24"/>
-      <c r="AE14" s="24"/>
-      <c r="AF14" s="24"/>
-      <c r="AG14" s="24"/>
-      <c r="AH14" s="24"/>
+      <c r="AA14" s="23"/>
+      <c r="AB14" s="23"/>
+      <c r="AC14" s="23"/>
+      <c r="AD14" s="23"/>
+      <c r="AE14" s="23"/>
+      <c r="AF14" s="23"/>
+      <c r="AG14" s="23"/>
+      <c r="AH14" s="23"/>
       <c r="AI14" s="22"/>
       <c r="AJ14" s="19" t="s">
         <v>10</v>
@@ -2732,38 +2726,38 @@
     <row r="15" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="17"/>
       <c r="B15" s="16"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
-      <c r="O15" s="24"/>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="24"/>
-      <c r="R15" s="24"/>
-      <c r="S15" s="24"/>
-      <c r="T15" s="24"/>
-      <c r="U15" s="24"/>
-      <c r="V15" s="24"/>
-      <c r="W15" s="24"/>
-      <c r="X15" s="24"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="23"/>
+      <c r="S15" s="23"/>
+      <c r="T15" s="23"/>
+      <c r="U15" s="23"/>
+      <c r="V15" s="23"/>
+      <c r="W15" s="23"/>
+      <c r="X15" s="23"/>
       <c r="Y15" s="21"/>
       <c r="Z15" s="21"/>
-      <c r="AA15" s="24"/>
-      <c r="AB15" s="24"/>
-      <c r="AC15" s="24"/>
-      <c r="AD15" s="24"/>
-      <c r="AE15" s="24"/>
-      <c r="AF15" s="24"/>
-      <c r="AG15" s="24"/>
-      <c r="AH15" s="24"/>
+      <c r="AA15" s="23"/>
+      <c r="AB15" s="23"/>
+      <c r="AC15" s="23"/>
+      <c r="AD15" s="23"/>
+      <c r="AE15" s="23"/>
+      <c r="AF15" s="23"/>
+      <c r="AG15" s="23"/>
+      <c r="AH15" s="23"/>
       <c r="AI15" s="22"/>
       <c r="AJ15" s="19" t="s">
         <v>10</v>
@@ -2776,38 +2770,38 @@
     <row r="16" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="17"/>
       <c r="B16" s="16"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
+      <c r="M16" s="23"/>
+      <c r="N16" s="23"/>
+      <c r="O16" s="23"/>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="23"/>
+      <c r="S16" s="23"/>
+      <c r="T16" s="23"/>
+      <c r="U16" s="23"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="23"/>
       <c r="Y16" s="21"/>
       <c r="Z16" s="21"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
-      <c r="AH16" s="24"/>
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="23"/>
+      <c r="AC16" s="23"/>
+      <c r="AD16" s="23"/>
+      <c r="AE16" s="23"/>
+      <c r="AF16" s="23"/>
+      <c r="AG16" s="23"/>
+      <c r="AH16" s="23"/>
       <c r="AI16" s="22"/>
       <c r="AJ16" s="19" t="s">
         <v>10</v>
@@ -2820,38 +2814,38 @@
     <row r="17" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17"/>
       <c r="B17" s="16"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+      <c r="L17" s="23"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="23"/>
+      <c r="O17" s="23"/>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="23"/>
+      <c r="S17" s="23"/>
+      <c r="T17" s="23"/>
+      <c r="U17" s="23"/>
+      <c r="V17" s="23"/>
+      <c r="W17" s="23"/>
+      <c r="X17" s="23"/>
       <c r="Y17" s="21"/>
       <c r="Z17" s="21"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="24"/>
-      <c r="AH17" s="24"/>
+      <c r="AA17" s="23"/>
+      <c r="AB17" s="23"/>
+      <c r="AC17" s="23"/>
+      <c r="AD17" s="23"/>
+      <c r="AE17" s="23"/>
+      <c r="AF17" s="23"/>
+      <c r="AG17" s="23"/>
+      <c r="AH17" s="23"/>
       <c r="AI17" s="20"/>
       <c r="AJ17" s="19" t="s">
         <v>10</v>
@@ -2864,38 +2858,38 @@
     <row r="18" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17"/>
       <c r="B18" s="16"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+      <c r="L18" s="23"/>
+      <c r="M18" s="23"/>
+      <c r="N18" s="23"/>
+      <c r="O18" s="23"/>
+      <c r="P18" s="23"/>
+      <c r="Q18" s="23"/>
+      <c r="R18" s="23"/>
+      <c r="S18" s="23"/>
+      <c r="T18" s="23"/>
+      <c r="U18" s="23"/>
+      <c r="V18" s="23"/>
+      <c r="W18" s="23"/>
+      <c r="X18" s="23"/>
       <c r="Y18" s="15"/>
       <c r="Z18" s="15"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="24"/>
-      <c r="AH18" s="24"/>
+      <c r="AA18" s="23"/>
+      <c r="AB18" s="23"/>
+      <c r="AC18" s="23"/>
+      <c r="AD18" s="23"/>
+      <c r="AE18" s="23"/>
+      <c r="AF18" s="23"/>
+      <c r="AG18" s="23"/>
+      <c r="AH18" s="23"/>
       <c r="AI18" s="15"/>
       <c r="AJ18" s="14" t="s">
         <v>10</v>
@@ -2908,38 +2902,38 @@
     <row r="19" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="17"/>
       <c r="B19" s="16"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="23"/>
+      <c r="W19" s="23"/>
+      <c r="X19" s="23"/>
       <c r="Y19" s="15"/>
       <c r="Z19" s="15"/>
-      <c r="AA19" s="24"/>
-      <c r="AB19" s="24"/>
-      <c r="AC19" s="24"/>
-      <c r="AD19" s="24"/>
-      <c r="AE19" s="24"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="24"/>
-      <c r="AH19" s="24"/>
+      <c r="AA19" s="23"/>
+      <c r="AB19" s="23"/>
+      <c r="AC19" s="23"/>
+      <c r="AD19" s="23"/>
+      <c r="AE19" s="23"/>
+      <c r="AF19" s="23"/>
+      <c r="AG19" s="23"/>
+      <c r="AH19" s="23"/>
       <c r="AI19" s="15"/>
       <c r="AJ19" s="14" t="s">
         <v>10</v>
@@ -2952,38 +2946,38 @@
     <row r="20" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="17"/>
       <c r="B20" s="16"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="23"/>
+      <c r="Q20" s="23"/>
+      <c r="R20" s="23"/>
+      <c r="S20" s="23"/>
+      <c r="T20" s="23"/>
+      <c r="U20" s="23"/>
+      <c r="V20" s="23"/>
+      <c r="W20" s="23"/>
+      <c r="X20" s="23"/>
       <c r="Y20" s="15"/>
       <c r="Z20" s="15"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
-      <c r="AH20" s="24"/>
+      <c r="AA20" s="23"/>
+      <c r="AB20" s="23"/>
+      <c r="AC20" s="23"/>
+      <c r="AD20" s="23"/>
+      <c r="AE20" s="23"/>
+      <c r="AF20" s="23"/>
+      <c r="AG20" s="23"/>
+      <c r="AH20" s="23"/>
       <c r="AI20" s="15"/>
       <c r="AJ20" s="14" t="s">
         <v>10</v>
@@ -2996,38 +2990,38 @@
     <row r="21" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="17"/>
       <c r="B21" s="16"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="23"/>
+      <c r="Q21" s="23"/>
+      <c r="R21" s="23"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="23"/>
+      <c r="U21" s="23"/>
+      <c r="V21" s="23"/>
+      <c r="W21" s="23"/>
+      <c r="X21" s="23"/>
       <c r="Y21" s="15"/>
       <c r="Z21" s="15"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
+      <c r="AA21" s="23"/>
+      <c r="AB21" s="23"/>
+      <c r="AC21" s="23"/>
+      <c r="AD21" s="23"/>
+      <c r="AE21" s="23"/>
+      <c r="AF21" s="23"/>
+      <c r="AG21" s="23"/>
+      <c r="AH21" s="23"/>
       <c r="AI21" s="15"/>
       <c r="AJ21" s="14" t="s">
         <v>10</v>
@@ -3040,38 +3034,38 @@
     <row r="22" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="17"/>
       <c r="B22" s="16"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="24"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="24"/>
-      <c r="S22" s="24"/>
-      <c r="T22" s="24"/>
-      <c r="U22" s="24"/>
-      <c r="V22" s="24"/>
-      <c r="W22" s="24"/>
-      <c r="X22" s="24"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="23"/>
+      <c r="X22" s="23"/>
       <c r="Y22" s="15"/>
       <c r="Z22" s="15"/>
-      <c r="AA22" s="24"/>
-      <c r="AB22" s="24"/>
-      <c r="AC22" s="24"/>
-      <c r="AD22" s="24"/>
-      <c r="AE22" s="24"/>
-      <c r="AF22" s="24"/>
-      <c r="AG22" s="24"/>
-      <c r="AH22" s="24"/>
+      <c r="AA22" s="23"/>
+      <c r="AB22" s="23"/>
+      <c r="AC22" s="23"/>
+      <c r="AD22" s="23"/>
+      <c r="AE22" s="23"/>
+      <c r="AF22" s="23"/>
+      <c r="AG22" s="23"/>
+      <c r="AH22" s="23"/>
       <c r="AI22" s="15"/>
       <c r="AJ22" s="14" t="s">
         <v>10</v>
@@ -3084,38 +3078,38 @@
     <row r="23" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="17"/>
       <c r="B23" s="16"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="24"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="24"/>
-      <c r="S23" s="24"/>
-      <c r="T23" s="24"/>
-      <c r="U23" s="24"/>
-      <c r="V23" s="24"/>
-      <c r="W23" s="24"/>
-      <c r="X23" s="24"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="23"/>
+      <c r="N23" s="23"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="23"/>
+      <c r="Q23" s="23"/>
+      <c r="R23" s="23"/>
+      <c r="S23" s="23"/>
+      <c r="T23" s="23"/>
+      <c r="U23" s="23"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="23"/>
+      <c r="X23" s="23"/>
       <c r="Y23" s="15"/>
       <c r="Z23" s="15"/>
-      <c r="AA23" s="24"/>
-      <c r="AB23" s="24"/>
-      <c r="AC23" s="24"/>
-      <c r="AD23" s="24"/>
-      <c r="AE23" s="24"/>
-      <c r="AF23" s="24"/>
-      <c r="AG23" s="24"/>
-      <c r="AH23" s="24"/>
+      <c r="AA23" s="23"/>
+      <c r="AB23" s="23"/>
+      <c r="AC23" s="23"/>
+      <c r="AD23" s="23"/>
+      <c r="AE23" s="23"/>
+      <c r="AF23" s="23"/>
+      <c r="AG23" s="23"/>
+      <c r="AH23" s="23"/>
       <c r="AI23" s="15"/>
       <c r="AJ23" s="14" t="s">
         <v>10</v>
@@ -3128,38 +3122,38 @@
     <row r="24" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="17"/>
       <c r="B24" s="16"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="24"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="24"/>
-      <c r="S24" s="24"/>
-      <c r="T24" s="24"/>
-      <c r="U24" s="24"/>
-      <c r="V24" s="24"/>
-      <c r="W24" s="24"/>
-      <c r="X24" s="24"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+      <c r="L24" s="23"/>
+      <c r="M24" s="23"/>
+      <c r="N24" s="23"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="23"/>
+      <c r="Q24" s="23"/>
+      <c r="R24" s="23"/>
+      <c r="S24" s="23"/>
+      <c r="T24" s="23"/>
+      <c r="U24" s="23"/>
+      <c r="V24" s="23"/>
+      <c r="W24" s="23"/>
+      <c r="X24" s="23"/>
       <c r="Y24" s="15"/>
       <c r="Z24" s="15"/>
-      <c r="AA24" s="24"/>
-      <c r="AB24" s="24"/>
-      <c r="AC24" s="24"/>
-      <c r="AD24" s="24"/>
-      <c r="AE24" s="24"/>
-      <c r="AF24" s="24"/>
-      <c r="AG24" s="24"/>
-      <c r="AH24" s="24"/>
+      <c r="AA24" s="23"/>
+      <c r="AB24" s="23"/>
+      <c r="AC24" s="23"/>
+      <c r="AD24" s="23"/>
+      <c r="AE24" s="23"/>
+      <c r="AF24" s="23"/>
+      <c r="AG24" s="23"/>
+      <c r="AH24" s="23"/>
       <c r="AI24" s="15"/>
       <c r="AJ24" s="14" t="s">
         <v>10</v>
@@ -3172,38 +3166,38 @@
     <row r="25" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="17"/>
       <c r="B25" s="16"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24"/>
-      <c r="Q25" s="24"/>
-      <c r="R25" s="24"/>
-      <c r="S25" s="24"/>
-      <c r="T25" s="24"/>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="23"/>
+      <c r="N25" s="23"/>
+      <c r="O25" s="23"/>
+      <c r="P25" s="23"/>
+      <c r="Q25" s="23"/>
+      <c r="R25" s="23"/>
+      <c r="S25" s="23"/>
+      <c r="T25" s="23"/>
+      <c r="U25" s="23"/>
+      <c r="V25" s="23"/>
+      <c r="W25" s="23"/>
+      <c r="X25" s="23"/>
       <c r="Y25" s="15"/>
       <c r="Z25" s="15"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
-      <c r="AC25" s="24"/>
-      <c r="AD25" s="24"/>
-      <c r="AE25" s="24"/>
-      <c r="AF25" s="24"/>
-      <c r="AG25" s="24"/>
-      <c r="AH25" s="24"/>
+      <c r="AA25" s="23"/>
+      <c r="AB25" s="23"/>
+      <c r="AC25" s="23"/>
+      <c r="AD25" s="23"/>
+      <c r="AE25" s="23"/>
+      <c r="AF25" s="23"/>
+      <c r="AG25" s="23"/>
+      <c r="AH25" s="23"/>
       <c r="AI25" s="15"/>
       <c r="AJ25" s="14" t="s">
         <v>10</v>
@@ -3216,38 +3210,38 @@
     <row r="26" spans="1:38" ht="32.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="17"/>
       <c r="B26" s="16"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24"/>
-      <c r="Q26" s="24"/>
-      <c r="R26" s="24"/>
-      <c r="S26" s="24"/>
-      <c r="T26" s="24"/>
-      <c r="U26" s="24"/>
-      <c r="V26" s="24"/>
-      <c r="W26" s="24"/>
-      <c r="X26" s="24"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="23"/>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+      <c r="L26" s="23"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="23"/>
+      <c r="O26" s="23"/>
+      <c r="P26" s="23"/>
+      <c r="Q26" s="23"/>
+      <c r="R26" s="23"/>
+      <c r="S26" s="23"/>
+      <c r="T26" s="23"/>
+      <c r="U26" s="23"/>
+      <c r="V26" s="23"/>
+      <c r="W26" s="23"/>
+      <c r="X26" s="23"/>
       <c r="Y26" s="15"/>
       <c r="Z26" s="15"/>
-      <c r="AA26" s="24"/>
-      <c r="AB26" s="24"/>
-      <c r="AC26" s="24"/>
-      <c r="AD26" s="24"/>
-      <c r="AE26" s="24"/>
-      <c r="AF26" s="24"/>
-      <c r="AG26" s="24"/>
-      <c r="AH26" s="24"/>
+      <c r="AA26" s="23"/>
+      <c r="AB26" s="23"/>
+      <c r="AC26" s="23"/>
+      <c r="AD26" s="23"/>
+      <c r="AE26" s="23"/>
+      <c r="AF26" s="23"/>
+      <c r="AG26" s="23"/>
+      <c r="AH26" s="23"/>
       <c r="AI26" s="15"/>
       <c r="AJ26" s="14" t="s">
         <v>10</v>
@@ -3258,86 +3252,86 @@
       <c r="AL26" s="7"/>
     </row>
     <row r="27" spans="1:38" s="8" customFormat="1" ht="409.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="45" t="s">
+      <c r="A27" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="46"/>
-      <c r="C27" s="46"/>
-      <c r="D27" s="46"/>
-      <c r="E27" s="46"/>
-      <c r="F27" s="46"/>
-      <c r="G27" s="46"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="46"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="46"/>
-      <c r="O27" s="46"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="46"/>
-      <c r="R27" s="46"/>
-      <c r="S27" s="46"/>
-      <c r="T27" s="46"/>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46"/>
-      <c r="X27" s="46"/>
-      <c r="Y27" s="46"/>
-      <c r="Z27" s="46"/>
-      <c r="AA27" s="46"/>
-      <c r="AB27" s="46"/>
-      <c r="AC27" s="46"/>
-      <c r="AD27" s="46"/>
-      <c r="AE27" s="46"/>
-      <c r="AF27" s="46"/>
-      <c r="AG27" s="46"/>
-      <c r="AH27" s="46"/>
-      <c r="AI27" s="46"/>
-      <c r="AJ27" s="46"/>
-      <c r="AK27" s="46"/>
-      <c r="AL27" s="47"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="27"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="27"/>
+      <c r="I27" s="27"/>
+      <c r="J27" s="27"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="27"/>
+      <c r="M27" s="27"/>
+      <c r="N27" s="27"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="27"/>
+      <c r="Q27" s="27"/>
+      <c r="R27" s="27"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="27"/>
+      <c r="U27" s="27"/>
+      <c r="V27" s="27"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
+      <c r="Y27" s="27"/>
+      <c r="Z27" s="27"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="27"/>
+      <c r="AC27" s="27"/>
+      <c r="AD27" s="27"/>
+      <c r="AE27" s="27"/>
+      <c r="AF27" s="27"/>
+      <c r="AG27" s="27"/>
+      <c r="AH27" s="27"/>
+      <c r="AI27" s="27"/>
+      <c r="AJ27" s="27"/>
+      <c r="AK27" s="27"/>
+      <c r="AL27" s="28"/>
     </row>
     <row r="28" spans="1:38" s="8" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A28" s="48"/>
-      <c r="B28" s="49"/>
-      <c r="C28" s="49"/>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49"/>
-      <c r="F28" s="49"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="49"/>
-      <c r="I28" s="49"/>
-      <c r="J28" s="49"/>
-      <c r="K28" s="49"/>
-      <c r="L28" s="49"/>
-      <c r="M28" s="49"/>
-      <c r="N28" s="49"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="49"/>
-      <c r="Q28" s="49"/>
-      <c r="R28" s="49"/>
-      <c r="S28" s="49"/>
-      <c r="T28" s="49"/>
-      <c r="U28" s="49"/>
-      <c r="V28" s="49"/>
-      <c r="W28" s="49"/>
-      <c r="X28" s="49"/>
-      <c r="Y28" s="49"/>
-      <c r="Z28" s="49"/>
-      <c r="AA28" s="49"/>
-      <c r="AB28" s="49"/>
-      <c r="AC28" s="49"/>
-      <c r="AD28" s="49"/>
-      <c r="AE28" s="49"/>
-      <c r="AF28" s="49"/>
-      <c r="AG28" s="49"/>
-      <c r="AH28" s="49"/>
-      <c r="AI28" s="49"/>
-      <c r="AJ28" s="49"/>
-      <c r="AK28" s="49"/>
-      <c r="AL28" s="50"/>
+      <c r="A28" s="29"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="30"/>
+      <c r="L28" s="30"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="30"/>
+      <c r="O28" s="30"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="30"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="30"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="30"/>
+      <c r="X28" s="30"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="30"/>
+      <c r="AA28" s="30"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="30"/>
+      <c r="AD28" s="30"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="30"/>
+      <c r="AG28" s="30"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="30"/>
+      <c r="AJ28" s="30"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="31"/>
     </row>
     <row r="29" spans="1:38" s="12" customFormat="1" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="9" t="s">
@@ -3351,44 +3345,44 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="51" t="s">
+      <c r="H29" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="I29" s="51"/>
-      <c r="J29" s="51"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
       <c r="O29" s="11"/>
-      <c r="P29" s="51" t="s">
+      <c r="P29" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
       <c r="S29" s="11"/>
       <c r="T29" s="11"/>
       <c r="U29" s="11"/>
-      <c r="V29" s="51" t="s">
+      <c r="V29" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="W29" s="51"/>
-      <c r="X29" s="51"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
       <c r="Y29" s="11"/>
       <c r="Z29" s="11"/>
       <c r="AA29" s="11"/>
-      <c r="AB29" s="51" t="s">
+      <c r="AB29" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="AC29" s="51"/>
-      <c r="AD29" s="51"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
       <c r="AE29" s="11"/>
       <c r="AF29" s="11"/>
       <c r="AG29" s="11"/>
-      <c r="AH29" s="55" t="s">
+      <c r="AH29" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="AI29" s="55"/>
+      <c r="AI29" s="54"/>
       <c r="AJ29" s="10"/>
       <c r="AK29" s="10"/>
       <c r="AL29" s="10"/>
@@ -3400,12 +3394,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A27:AL28"/>
-    <mergeCell ref="H29:J29"/>
-    <mergeCell ref="P29:R29"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="AB29:AD29"/>
-    <mergeCell ref="AH29:AI29"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="X1:AL2"/>
     <mergeCell ref="A2:W2"/>
@@ -3417,6 +3405,12 @@
     <mergeCell ref="AJ3:AJ4"/>
     <mergeCell ref="AK3:AK4"/>
     <mergeCell ref="AL3:AL4"/>
+    <mergeCell ref="A27:AL28"/>
+    <mergeCell ref="H29:J29"/>
+    <mergeCell ref="P29:R29"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="AB29:AD29"/>
+    <mergeCell ref="AH29:AI29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
